--- a/Data Dictionary.xlsx
+++ b/Data Dictionary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="5" activeTab="13"/>
+    <workbookView windowWidth="13272" windowHeight="8400" firstSheet="10" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Customers.csv" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="251">
   <si>
     <t>STT</t>
   </si>
@@ -672,18 +672,99 @@
     <t>Mã chương trình khuyến mãi thứ hai (bổ sung) được áp dụng đồng thời cho đơn hàng, dạng 'PROMO-xxxx'. Phần lớn giá trị trống (NULL).</t>
   </si>
   <si>
+    <t>Integer (int64)</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất của đơn hàng, dùng để liên kết với các bảng khác (ví dụ: bảng đơn hàng, khách hàng)</t>
+  </si>
+  <si>
+    <t>String (text)</t>
+  </si>
+  <si>
+    <t>Phương thức thanh toán được sử dụng cho đơn hàng, gồm 5 giá trị: credit_card (thẻ tín dụng), cod (thanh toán khi nhận hàng), paypal, apple_pay, bank_transfer (chuyển khoản ngân hàng)</t>
+  </si>
+  <si>
+    <t>payment_value</t>
+  </si>
+  <si>
+    <t>Float (số thực)</t>
+  </si>
+  <si>
+    <t>Giá trị/số tiền thanh toán cho đơn hàng (đơn vị tiền tệ), dao động từ khoảng 389.74 đến 331,570.4</t>
+  </si>
+  <si>
+    <t>installments</t>
+  </si>
+  <si>
+    <t>Số kỳ trả góp của đơn hàng, giá trị từ 1 (thanh toán 1 lần) đến 12 kỳ</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất của chương trình khuyến mãi (ví dụ: PROMO-0001)</t>
+  </si>
+  <si>
+    <t>Tên chương trình khuyến mãi (ví dụ: Spring Sale 2013)</t>
+  </si>
+  <si>
+    <t>Loại khuyến mãi, gồm 2 giá trị: percentage (giảm theo %), fixed (giảm theo số tiền cố định)</t>
+  </si>
+  <si>
+    <t>Giá trị giảm giá, dao động từ 10 đến 50 (đơn vị theo promo_type: % hoặc số tiền)</t>
+  </si>
+  <si>
+    <t>String (date)</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu áp dụng khuyến mãi (định dạng YYYY-MM-DD), từ 2013-01-31</t>
+  </si>
+  <si>
+    <t>Ngày kết thúc áp dụng khuyến mãi (định dạng YYYY-MM-DD), đến 2022-11-18</t>
+  </si>
+  <si>
+    <t>Danh mục sản phẩm được áp dụng khuyến mãi: Streetwear, Outdoor, hoặc rỗng/NaN (áp dụng cho tất cả danh mục)</t>
+  </si>
+  <si>
+    <t>Kênh áp dụng khuyến mãi, gồm 5 giá trị: email, online, all_channels, in_store, social_media</t>
+  </si>
+  <si>
+    <t>Integer (0/1)</t>
+  </si>
+  <si>
+    <t>Cờ đánh dấu khuyến mãi có thể cộng dồn với khuyến mãi khác hay không (1 = có thể, 0 = không thể)</t>
+  </si>
+  <si>
+    <t>Giá trị đơn hàng tối thiểu để được áp dụng khuyến mãi (0 nghĩa là không yêu cầu tối thiểu), tối đa 200,000</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất của sản phẩm</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm (ví dụ: SaigonFlex UC-01), gồm 2,172 tên khác nhau</t>
+  </si>
+  <si>
+    <t>Danh mục sản phẩm, gồm 4 giá trị: Streetwear, Casual, Outdoor, GenZ</t>
+  </si>
+  <si>
+    <t>Phân khúc/dòng sản phẩm, gồm 8 giá trị: Everyday, Performance, Balanced, Standard, All-weather, Premium, Trendy, Activewear</t>
+  </si>
+  <si>
+    <t>Kích cỡ sản phẩm, gồm 4 giá trị: S, M, L, XL</t>
+  </si>
+  <si>
+    <t>Màu sắc sản phẩm, gồm 10 màu (green, silver, pink, yellow, red, black, orange, blue, white, purple)</t>
+  </si>
+  <si>
+    <t>Giá bán của sản phẩm, dao động từ khoảng 9.06 đến 40,950</t>
+  </si>
+  <si>
+    <t>Giá vốn hàng bán (Cost of Goods Sold) của sản phẩm, dao động từ khoảng 5.18 đến 38,902.5</t>
+  </si>
+  <si>
     <t>return_id</t>
   </si>
   <si>
-    <t>String (text)</t>
-  </si>
-  <si>
     <t>Mã định danh duy nhất của lượt trả hàng (ví dụ: RET-000001)</t>
   </si>
   <si>
-    <t>Integer (int64)</t>
-  </si>
-  <si>
     <t>Mã đơn hàng liên quan đến lượt trả hàng, dùng để liên kết với bảng đơn hàng</t>
   </si>
   <si>
@@ -693,9 +774,6 @@
     <t>return_date</t>
   </si>
   <si>
-    <t>String (date)</t>
-  </si>
-  <si>
     <t>Ngày thực hiện trả hàng (định dạng YYYY-MM-DD), từ 2012-07-11 đến 2022-12-31</t>
   </si>
   <si>
@@ -714,67 +792,7 @@
     <t>refund_amount</t>
   </si>
   <si>
-    <t>Float (số thực)</t>
-  </si>
-  <si>
     <t>Số tiền hoàn trả cho lượt trả hàng, dao động từ khoảng 458.81 đến 160,937.94</t>
-  </si>
-  <si>
-    <t>Mã định danh duy nhất của chương trình khuyến mãi (ví dụ: PROMO-0001)</t>
-  </si>
-  <si>
-    <t>Tên chương trình khuyến mãi (ví dụ: Spring Sale 2013)</t>
-  </si>
-  <si>
-    <t>Loại khuyến mãi, gồm 2 giá trị: percentage (giảm theo %), fixed (giảm theo số tiền cố định)</t>
-  </si>
-  <si>
-    <t>Giá trị giảm giá, dao động từ 10 đến 50 (đơn vị theo promo_type: % hoặc số tiền)</t>
-  </si>
-  <si>
-    <t>Ngày bắt đầu áp dụng khuyến mãi (định dạng YYYY-MM-DD), từ 2013-01-31</t>
-  </si>
-  <si>
-    <t>Ngày kết thúc áp dụng khuyến mãi (định dạng YYYY-MM-DD), đến 2022-11-18</t>
-  </si>
-  <si>
-    <t>Danh mục sản phẩm được áp dụng khuyến mãi: Streetwear, Outdoor, hoặc rỗng/NaN (áp dụng cho tất cả danh mục)</t>
-  </si>
-  <si>
-    <t>Kênh áp dụng khuyến mãi, gồm 5 giá trị: email, online, all_channels, in_store, social_media</t>
-  </si>
-  <si>
-    <t>Integer (0/1)</t>
-  </si>
-  <si>
-    <t>Cờ đánh dấu khuyến mãi có thể cộng dồn với khuyến mãi khác hay không (1 = có thể, 0 = không thể)</t>
-  </si>
-  <si>
-    <t>Giá trị đơn hàng tối thiểu để được áp dụng khuyến mãi (0 nghĩa là không yêu cầu tối thiểu), tối đa 200,000</t>
-  </si>
-  <si>
-    <t>Mã định danh duy nhất của sản phẩm</t>
-  </si>
-  <si>
-    <t>Tên sản phẩm (ví dụ: SaigonFlex UC-01), gồm 2,172 tên khác nhau</t>
-  </si>
-  <si>
-    <t>Danh mục sản phẩm, gồm 4 giá trị: Streetwear, Casual, Outdoor, GenZ</t>
-  </si>
-  <si>
-    <t>Phân khúc/dòng sản phẩm, gồm 8 giá trị: Everyday, Performance, Balanced, Standard, All-weather, Premium, Trendy, Activewear</t>
-  </si>
-  <si>
-    <t>Kích cỡ sản phẩm, gồm 4 giá trị: S, M, L, XL</t>
-  </si>
-  <si>
-    <t>Màu sắc sản phẩm, gồm 10 màu (green, silver, pink, yellow, red, black, orange, blue, white, purple)</t>
-  </si>
-  <si>
-    <t>Giá bán của sản phẩm, dao động từ khoảng 9.06 đến 40,950</t>
-  </si>
-  <si>
-    <t>Giá vốn hàng bán (Cost of Goods Sold) của sản phẩm, dao động từ khoảng 5.18 đến 38,902.5</t>
   </si>
 </sst>
 </file>
@@ -796,6 +814,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -830,13 +855,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1478,7 +1496,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1488,43 +1506,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2058,122 +2079,122 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="6.77777777777778" style="14" customWidth="1"/>
+    <col min="1" max="1" width="6.77777777777778" style="16" customWidth="1"/>
     <col min="2" max="2" width="27.8888888888889" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.6666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="66.4444444444444" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="17.4" spans="1:4">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:4">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="16">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="16">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="16">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="16">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="16">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="16">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2195,91 +2216,91 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" ht="72" spans="1:3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>209</v>
       </c>
     </row>
@@ -2302,92 +2323,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:3">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="54" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" ht="90" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="3" ht="36" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" ht="54" spans="1:3">
+      <c r="A4" s="5" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="5" ht="54" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="5" ht="36" spans="1:3">
+      <c r="A5" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="6" ht="90" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" ht="36" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>225</v>
-      </c>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2407,7 +2410,7 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.2" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2418,114 +2421,114 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="252" spans="1:3">
+    <row r="2" ht="36" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" ht="162" spans="1:3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" ht="36" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="4" ht="270" spans="1:3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" ht="54" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" ht="198" spans="1:3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" ht="36" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" ht="234" spans="1:3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" ht="36" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" ht="252" spans="1:3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" ht="36" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="8" ht="342" spans="1:3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" ht="54" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" ht="270" spans="1:3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" ht="54" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="10" ht="306" spans="1:3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" ht="54" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" ht="324" spans="1:3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" ht="54" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2546,7 +2549,7 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.2" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2557,92 +2560,92 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="126" spans="1:3">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" ht="216" spans="1:3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" ht="36" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" ht="198" spans="1:3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" ht="36" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="5" ht="396" spans="1:3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" ht="54" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" ht="126" spans="1:3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" ht="270" spans="1:3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" ht="36" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" ht="162" spans="1:3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" ht="306" spans="1:3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" ht="36" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2666,7 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.2" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2674,81 +2677,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="216" spans="1:3">
+    <row r="2" ht="36" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" ht="234" spans="1:3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" ht="54" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" ht="180" spans="1:3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" ht="36" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" ht="54" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" ht="108" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" ht="36" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" ht="54" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="5" ht="252" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" ht="409.5" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" ht="144" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" ht="216" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -2769,102 +2772,102 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:3">
+      <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="15" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2887,124 +2890,124 @@
     <col min="5" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:3">
+      <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="15" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3027,90 +3030,90 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.15" spans="1:3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" ht="18.75" spans="1:3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" ht="18.75" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="12" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" ht="37" customHeight="1" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" ht="18.75" spans="1:3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3133,255 +3136,255 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.15" spans="1:3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" ht="18.75" spans="1:3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:3">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="18.75" spans="1:3">
+      <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="12" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="6" ht="18.75" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" ht="36.75" spans="1:3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="8" ht="36.75" spans="1:3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" ht="36.75" spans="1:3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" ht="36.75" spans="1:3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" ht="36.75" spans="1:3">
-      <c r="A11" s="10" t="s">
+    <row r="11" ht="36" spans="1:3">
+      <c r="A11" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="12" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" ht="36.75" spans="1:3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="12" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="13" ht="36.75" spans="1:3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="12" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="14" ht="36.75" spans="1:3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" ht="18.75" spans="1:3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="16" ht="18.75" spans="1:3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" ht="18.75" spans="1:3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="18" ht="18.75" spans="1:3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="19" ht="18.75" spans="1:3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="20" ht="36.75" spans="1:3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="21" ht="18.75" spans="1:3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="22" ht="18.75" spans="1:3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="23" ht="18.75" spans="1:3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="12" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3403,91 +3406,91 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="18.15" spans="1:3">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="10" customFormat="1" ht="18.15" spans="1:3">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="90.75" spans="1:3">
-      <c r="A2" s="10" t="s">
+    <row r="2" ht="72.75" spans="1:3">
+      <c r="A2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="3" ht="54.75" spans="1:3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="7" ht="36.75" spans="1:3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="8" ht="54.75" spans="1:3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3506,58 +3509,58 @@
     <col min="1" max="16384" width="42.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="5" ht="67" customHeight="1" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3578,201 +3581,201 @@
     <col min="3" max="3" width="47.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="9" customFormat="1" ht="17.4" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" ht="54" spans="1:3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" ht="54" spans="1:3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="17" ht="36" spans="1:3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3794,201 +3797,201 @@
     <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="11" ht="36" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" ht="90" spans="1:3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" ht="36" spans="1:3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="16" ht="54" spans="1:3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="17" ht="54" spans="1:3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>198</v>
       </c>
     </row>

--- a/Data Dictionary.xlsx
+++ b/Data Dictionary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13272" windowHeight="8400" firstSheet="10" activeTab="10"/>
+    <workbookView windowWidth="13272" windowHeight="9000" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Customers.csv" sheetId="1" r:id="rId1"/>
